--- a/300.xlsx
+++ b/300.xlsx
@@ -511,7 +511,7 @@
         <v>0.4524632692337036</v>
       </c>
       <c r="K2" t="n">
-        <v>1.587500000005093e-05</v>
+        <v>1.503279999997176e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.4351803958415985</v>
       </c>
       <c r="K3" t="n">
-        <v>1.006919999963429e-05</v>
+        <v>1.027849999991304e-05</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.447928249835968</v>
       </c>
       <c r="K4" t="n">
-        <v>9.856800000306975e-06</v>
+        <v>1.031379999949422e-05</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.4653018116950989</v>
       </c>
       <c r="K5" t="n">
-        <v>9.841600000072503e-06</v>
+        <v>1.071369999954186e-05</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.446069210767746</v>
       </c>
       <c r="K6" t="n">
-        <v>1.065139999991516e-05</v>
+        <v>9.697800000139978e-06</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.4901336133480072</v>
       </c>
       <c r="K7" t="n">
-        <v>9.81599999977334e-06</v>
+        <v>1.225239999985206e-05</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.4944420158863068</v>
       </c>
       <c r="K8" t="n">
-        <v>9.720900000502298e-06</v>
+        <v>9.663400000135881e-06</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.4927139282226562</v>
       </c>
       <c r="K9" t="n">
-        <v>9.727699999530159e-06</v>
+        <v>9.999500000049011e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.496104896068573</v>
       </c>
       <c r="K10" t="n">
-        <v>1.154570000016975e-05</v>
+        <v>1.096660000075644e-05</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.4914999008178711</v>
       </c>
       <c r="K11" t="n">
-        <v>9.81210000009014e-06</v>
+        <v>1.019509999969159e-05</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.4931358695030212</v>
       </c>
       <c r="K12" t="n">
-        <v>9.663799999543699e-06</v>
+        <v>1.038020000123652e-05</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.4937478005886078</v>
       </c>
       <c r="K13" t="n">
-        <v>9.456800000407385e-06</v>
+        <v>1.000539999949979e-05</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.496439665555954</v>
       </c>
       <c r="K14" t="n">
-        <v>9.990399999878719e-06</v>
+        <v>1.020210000024235e-05</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.4954337775707245</v>
       </c>
       <c r="K15" t="n">
-        <v>9.927300000526884e-06</v>
+        <v>1.034500000059779e-05</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.4957082271575928</v>
       </c>
       <c r="K16" t="n">
-        <v>9.553199999572826e-06</v>
+        <v>9.797900000194204e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.4611021280288696</v>
       </c>
       <c r="K17" t="n">
-        <v>2.384150000034424e-05</v>
+        <v>2.257769999960146e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.4966996610164642</v>
       </c>
       <c r="K18" t="n">
-        <v>2.340860000003886e-05</v>
+        <v>2.406089999931282e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.4683510661125183</v>
       </c>
       <c r="K19" t="n">
-        <v>2.153209999960382e-05</v>
+        <v>2.197960000012245e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.5770438313484192</v>
       </c>
       <c r="K20" t="n">
-        <v>2.416320000065752e-05</v>
+        <v>2.179439999963506e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.461920827627182</v>
       </c>
       <c r="K21" t="n">
-        <v>2.291319999949337e-05</v>
+        <v>2.357459999984712e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.7016832232475281</v>
       </c>
       <c r="K22" t="n">
-        <v>2.089129999967554e-05</v>
+        <v>2.206400000068243e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.6908981204032898</v>
       </c>
       <c r="K23" t="n">
-        <v>2.434170000015001e-05</v>
+        <v>2.205150000008871e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.6801029443740845</v>
       </c>
       <c r="K24" t="n">
-        <v>2.423550000003161e-05</v>
+        <v>2.267039999969711e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.6816705465316772</v>
       </c>
       <c r="K25" t="n">
-        <v>2.169630000025791e-05</v>
+        <v>2.139630000056059e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.7020230889320374</v>
       </c>
       <c r="K26" t="n">
-        <v>2.307389999987208e-05</v>
+        <v>2.217869999913091e-05</v>
       </c>
     </row>
   </sheetData>

--- a/300.xlsx
+++ b/300.xlsx
@@ -511,7 +511,7 @@
         <v>0.4524632692337036</v>
       </c>
       <c r="K2" t="n">
-        <v>1.503279999997176e-05</v>
+        <v>1.683449999973163e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.4351803958415985</v>
       </c>
       <c r="K3" t="n">
-        <v>1.027849999991304e-05</v>
+        <v>1.12635999998929e-05</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.447928249835968</v>
       </c>
       <c r="K4" t="n">
-        <v>1.031379999949422e-05</v>
+        <v>1.128229999994801e-05</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.4653018116950989</v>
       </c>
       <c r="K5" t="n">
-        <v>1.071369999954186e-05</v>
+        <v>1.113489999988815e-05</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.446069210767746</v>
       </c>
       <c r="K6" t="n">
-        <v>9.697800000139978e-06</v>
+        <v>1.11363999999412e-05</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.4901336133480072</v>
       </c>
       <c r="K7" t="n">
-        <v>1.225239999985206e-05</v>
+        <v>1.125090000005002e-05</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.4944420158863068</v>
       </c>
       <c r="K8" t="n">
-        <v>9.663400000135881e-06</v>
+        <v>1.059900000018388e-05</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.4927139282226562</v>
       </c>
       <c r="K9" t="n">
-        <v>9.999500000049011e-06</v>
+        <v>1.105680000000575e-05</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.496104896068573</v>
       </c>
       <c r="K10" t="n">
-        <v>1.096660000075644e-05</v>
+        <v>1.287950000005367e-05</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.4914999008178711</v>
       </c>
       <c r="K11" t="n">
-        <v>1.019509999969159e-05</v>
+        <v>1.061989999971047e-05</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.4931358695030212</v>
       </c>
       <c r="K12" t="n">
-        <v>1.038020000123652e-05</v>
+        <v>1.072859999976572e-05</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.4937478005886078</v>
       </c>
       <c r="K13" t="n">
-        <v>1.000539999949979e-05</v>
+        <v>1.146030000018072e-05</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.496439665555954</v>
       </c>
       <c r="K14" t="n">
-        <v>1.020210000024235e-05</v>
+        <v>1.103869999997187e-05</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.4954337775707245</v>
       </c>
       <c r="K15" t="n">
-        <v>1.034500000059779e-05</v>
+        <v>1.056799999969371e-05</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.4957082271575928</v>
       </c>
       <c r="K16" t="n">
-        <v>9.797900000194204e-06</v>
+        <v>1.12779999999475e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.4611021280288696</v>
       </c>
       <c r="K17" t="n">
-        <v>2.257769999960146e-05</v>
+        <v>2.644710000004125e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.4966996610164642</v>
       </c>
       <c r="K18" t="n">
-        <v>2.406089999931282e-05</v>
+        <v>2.74648999998135e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.4683510661125183</v>
       </c>
       <c r="K19" t="n">
-        <v>2.197960000012245e-05</v>
+        <v>2.500250000002779e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.5770438313484192</v>
       </c>
       <c r="K20" t="n">
-        <v>2.179439999963506e-05</v>
+        <v>2.797599999985323e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.461920827627182</v>
       </c>
       <c r="K21" t="n">
-        <v>2.357459999984712e-05</v>
+        <v>2.744580000035057e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.7016832232475281</v>
       </c>
       <c r="K22" t="n">
-        <v>2.206400000068243e-05</v>
+        <v>2.449520000027405e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.6908981204032898</v>
       </c>
       <c r="K23" t="n">
-        <v>2.205150000008871e-05</v>
+        <v>2.776889999995546e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.6801029443740845</v>
       </c>
       <c r="K24" t="n">
-        <v>2.267039999969711e-05</v>
+        <v>2.727639999966414e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.6816705465316772</v>
       </c>
       <c r="K25" t="n">
-        <v>2.139630000056059e-05</v>
+        <v>2.432610000005297e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.7020230889320374</v>
       </c>
       <c r="K26" t="n">
-        <v>2.217869999913091e-05</v>
+        <v>2.806380000038189e-05</v>
       </c>
     </row>
   </sheetData>

--- a/300.xlsx
+++ b/300.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,20 +486,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>517.82 (11.95)</t>
+          <t>517.82</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.63044548034668</v>
+        <v>23.5144716129303</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9816862344741821</v>
+        <v>0.9816862769126892</v>
       </c>
       <c r="F2" t="n">
-        <v>0.876578688621521</v>
+        <v>0.8765786870718002</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03664526343345642</v>
+        <v>0.03664525984227657</v>
       </c>
       <c r="H2" t="n">
         <v>1.03788697719574</v>
@@ -511,7 +511,7 @@
         <v>0.4524632692337036</v>
       </c>
       <c r="K2" t="n">
-        <v>1.683449999973163e-05</v>
+        <v>5.51408999999694e-05</v>
       </c>
     </row>
     <row r="3">
@@ -527,20 +527,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>543.47 (12.45)</t>
+          <t>543.47</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.61324310302734</v>
+        <v>23.50281911277771</v>
       </c>
       <c r="E3" t="n">
-        <v>1.009835243225098</v>
+        <v>1.009835240721703</v>
       </c>
       <c r="F3" t="n">
         <v>0.8767573237419128</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03745225816965103</v>
+        <v>0.03745225444436073</v>
       </c>
       <c r="H3" t="n">
         <v>0.5733728408813477</v>
@@ -552,7 +552,7 @@
         <v>0.4351803958415985</v>
       </c>
       <c r="K3" t="n">
-        <v>1.12635999998929e-05</v>
+        <v>0.0001060106999998425</v>
       </c>
     </row>
     <row r="4">
@@ -568,20 +568,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>568.33 (12.93)</t>
+          <t>568.33</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.6240234375</v>
+        <v>23.5105962600708</v>
       </c>
       <c r="E4" t="n">
-        <v>1.047832250595093</v>
+        <v>1.047832258105278</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8638808131217957</v>
+        <v>0.8638807884454727</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03905914723873138</v>
+        <v>0.0390591447763145</v>
       </c>
       <c r="H4" t="n">
         <v>0.7450600862503052</v>
@@ -593,7 +593,7 @@
         <v>0.447928249835968</v>
       </c>
       <c r="K4" t="n">
-        <v>1.128229999994801e-05</v>
+        <v>4.161999999996624e-05</v>
       </c>
     </row>
     <row r="5">
@@ -609,20 +609,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>531.77 (12.22)</t>
+          <t>531.77</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>23.60359954833984</v>
+        <v>23.50681049728394</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9904959201812744</v>
+        <v>0.9904959365129471</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8835998177528381</v>
+        <v>0.883599758207798</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04204989969730377</v>
+        <v>0.04204990343749523</v>
       </c>
       <c r="H5" t="n">
         <v>0.9863747954368591</v>
@@ -634,7 +634,7 @@
         <v>0.4653018116950989</v>
       </c>
       <c r="K5" t="n">
-        <v>1.113489999988815e-05</v>
+        <v>3.61920000000282e-05</v>
       </c>
     </row>
     <row r="6">
@@ -650,20 +650,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>529.48 (12.18)</t>
+          <t>529.48</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23.60688591003418</v>
+        <v>23.49596078491211</v>
       </c>
       <c r="E6" t="n">
-        <v>0.992384672164917</v>
+        <v>0.9923847692012787</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8796173930168152</v>
+        <v>0.8796173926591874</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03738336637616158</v>
+        <v>0.03738335910812021</v>
       </c>
       <c r="H6" t="n">
         <v>0.8094307780265808</v>
@@ -675,7 +675,7 @@
         <v>0.446069210767746</v>
       </c>
       <c r="K6" t="n">
-        <v>1.11363999999412e-05</v>
+        <v>3.99029000000155e-05</v>
       </c>
     </row>
     <row r="7">
@@ -691,20 +691,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>516.51 (11.93)</t>
+          <t>516.51</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>305.2129821777344</v>
+        <v>305.1650648803711</v>
       </c>
       <c r="E7" t="n">
-        <v>10.86353492736816</v>
+        <v>10.86353600883484</v>
       </c>
       <c r="F7" t="n">
-        <v>76053.8984375</v>
+        <v>76053.895125</v>
       </c>
       <c r="G7" t="n">
-        <v>47.88793563842773</v>
+        <v>47.8879487953186</v>
       </c>
       <c r="H7" t="n">
         <v>0.5829544067382812</v>
@@ -716,7 +716,7 @@
         <v>0.4901336133480072</v>
       </c>
       <c r="K7" t="n">
-        <v>1.125090000005002e-05</v>
+        <v>3.236859999969966e-05</v>
       </c>
     </row>
     <row r="8">
@@ -732,14 +732,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>521.19 (12.02)</t>
+          <t>521.19</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>300.1514282226562</v>
+        <v>300.1035167236328</v>
       </c>
       <c r="E8" t="n">
-        <v>10.81852340698242</v>
+        <v>10.81852273845673</v>
       </c>
       <c r="F8" t="n">
         <v>73560.59375</v>
@@ -757,7 +757,7 @@
         <v>0.4944420158863068</v>
       </c>
       <c r="K8" t="n">
-        <v>1.059900000018388e-05</v>
+        <v>3.634079999983442e-05</v>
       </c>
     </row>
     <row r="9">
@@ -773,20 +773,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>520.88 (12.01)</t>
+          <t>520.88</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>297.3395080566406</v>
+        <v>297.2915965881348</v>
       </c>
       <c r="E9" t="n">
-        <v>10.81648349761963</v>
+        <v>10.81648396587372</v>
       </c>
       <c r="F9" t="n">
         <v>72244.734375</v>
       </c>
       <c r="G9" t="n">
-        <v>44.34444046020508</v>
+        <v>44.34444427490234</v>
       </c>
       <c r="H9" t="n">
         <v>0.584128201007843</v>
@@ -798,7 +798,7 @@
         <v>0.4927139282226562</v>
       </c>
       <c r="K9" t="n">
-        <v>1.105680000000575e-05</v>
+        <v>3.787669999974242e-05</v>
       </c>
     </row>
     <row r="10">
@@ -814,20 +814,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>522.77 (12.05)</t>
+          <t>522.77</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>301.5755920410156</v>
+        <v>301.5276805725098</v>
       </c>
       <c r="E10" t="n">
-        <v>10.8446741104126</v>
+        <v>10.84467466545105</v>
       </c>
       <c r="F10" t="n">
         <v>74250.671875</v>
       </c>
       <c r="G10" t="n">
-        <v>45.35451126098633</v>
+        <v>45.35451889038086</v>
       </c>
       <c r="H10" t="n">
         <v>0.5810527801513672</v>
@@ -839,7 +839,7 @@
         <v>0.496104896068573</v>
       </c>
       <c r="K10" t="n">
-        <v>1.287950000005367e-05</v>
+        <v>3.695470000002388e-05</v>
       </c>
     </row>
     <row r="11">
@@ -855,20 +855,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>520.91 (12.01)</t>
+          <t>520.91</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>301.6357421875</v>
+        <v>301.5878306884766</v>
       </c>
       <c r="E11" t="n">
-        <v>10.8266487121582</v>
+        <v>10.82664805030823</v>
       </c>
       <c r="F11" t="n">
         <v>74250.3359375</v>
       </c>
       <c r="G11" t="n">
-        <v>45.37546539306641</v>
+        <v>45.37547302246094</v>
       </c>
       <c r="H11" t="n">
         <v>0.5817579030990601</v>
@@ -880,7 +880,7 @@
         <v>0.4914999008178711</v>
       </c>
       <c r="K11" t="n">
-        <v>1.061989999971047e-05</v>
+        <v>4.095939999979237e-05</v>
       </c>
     </row>
     <row r="12">
@@ -896,20 +896,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>500.87 (11.62)</t>
+          <t>500.87</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>310.9536437988281</v>
+        <v>310.904331237793</v>
       </c>
       <c r="E12" t="n">
-        <v>10.87734508514404</v>
+        <v>10.87734477138519</v>
       </c>
       <c r="F12" t="n">
-        <v>78727.03125</v>
+        <v>78721.37654687501</v>
       </c>
       <c r="G12" t="n">
-        <v>49.68899154663086</v>
+        <v>49.68900030899048</v>
       </c>
       <c r="H12" t="n">
         <v>0.5797107815742493</v>
@@ -921,7 +921,7 @@
         <v>0.4931358695030212</v>
       </c>
       <c r="K12" t="n">
-        <v>1.072859999976572e-05</v>
+        <v>4.085250000025553e-05</v>
       </c>
     </row>
     <row r="13">
@@ -937,20 +937,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>502.11 (11.65)</t>
+          <t>502.11</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>313.7864685058594</v>
+        <v>313.7385570373535</v>
       </c>
       <c r="E13" t="n">
-        <v>10.84992790222168</v>
+        <v>10.84992753982544</v>
       </c>
       <c r="F13" t="n">
         <v>79825.828125</v>
       </c>
       <c r="G13" t="n">
-        <v>51.64237594604492</v>
+        <v>51.64238357543945</v>
       </c>
       <c r="H13" t="n">
         <v>0.5763192772865295</v>
@@ -962,7 +962,7 @@
         <v>0.4937478005886078</v>
       </c>
       <c r="K13" t="n">
-        <v>1.146030000018072e-05</v>
+        <v>3.480050000007396e-05</v>
       </c>
     </row>
     <row r="14">
@@ -978,20 +978,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>504.39 (11.69)</t>
+          <t>504.39</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>309.8309936523438</v>
+        <v>309.7830821533203</v>
       </c>
       <c r="E14" t="n">
-        <v>10.9078893661499</v>
+        <v>10.90788943195343</v>
       </c>
       <c r="F14" t="n">
         <v>78250.234375</v>
       </c>
       <c r="G14" t="n">
-        <v>48.18771362304688</v>
+        <v>48.18770980834961</v>
       </c>
       <c r="H14" t="n">
         <v>0.579704761505127</v>
@@ -1003,7 +1003,7 @@
         <v>0.496439665555954</v>
       </c>
       <c r="K14" t="n">
-        <v>1.103869999997187e-05</v>
+        <v>3.363360000003013e-05</v>
       </c>
     </row>
     <row r="15">
@@ -1019,14 +1019,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>505.22 (11.71)</t>
+          <t>505.22</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>312.1284790039062</v>
+        <v>312.0805675048828</v>
       </c>
       <c r="E15" t="n">
-        <v>10.81918334960938</v>
+        <v>10.8191839094162</v>
       </c>
       <c r="F15" t="n">
         <v>79110.859375</v>
@@ -1044,7 +1044,7 @@
         <v>0.4954337775707245</v>
       </c>
       <c r="K15" t="n">
-        <v>1.056799999969371e-05</v>
+        <v>3.952019999996991e-05</v>
       </c>
     </row>
     <row r="16">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>501.63 (11.64)</t>
+          <t>501.63</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>312.3099670410156</v>
+        <v>312.2620555725098</v>
       </c>
       <c r="E16" t="n">
-        <v>10.86781215667725</v>
+        <v>10.86781303405762</v>
       </c>
       <c r="F16" t="n">
         <v>79263.625</v>
       </c>
       <c r="G16" t="n">
-        <v>50.27367782592773</v>
+        <v>50.27366638183594</v>
       </c>
       <c r="H16" t="n">
         <v>0.5775067806243896</v>
@@ -1085,7 +1085,7 @@
         <v>0.4957082271575928</v>
       </c>
       <c r="K16" t="n">
-        <v>1.12779999999475e-05</v>
+        <v>3.971510000019407e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1101,20 +1101,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>507.23 (11.75)</t>
+          <t>507.23</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>23.64147567749023</v>
+        <v>23.51910361099243</v>
       </c>
       <c r="E17" t="n">
-        <v>0.994174063205719</v>
+        <v>0.9941741064786911</v>
       </c>
       <c r="F17" t="n">
         <v>0.05222225189208984</v>
       </c>
       <c r="G17" t="n">
-        <v>0.000313800061121583</v>
+        <v>0.0003138000029139221</v>
       </c>
       <c r="H17" t="n">
         <v>0.1645958572626114</v>
@@ -1126,7 +1126,7 @@
         <v>0.4611021280288696</v>
       </c>
       <c r="K17" t="n">
-        <v>2.644710000004125e-05</v>
+        <v>8.652249999977357e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1142,20 +1142,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>520.19 (12.00)</t>
+          <t>520.19</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>23.63478469848633</v>
+        <v>23.51423371505737</v>
       </c>
       <c r="E18" t="n">
-        <v>1.002053380012512</v>
+        <v>1.002053455770016</v>
       </c>
       <c r="F18" t="n">
         <v>0.04766607284545898</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0001393374841427431</v>
+        <v>0.0001393374986946583</v>
       </c>
       <c r="H18" t="n">
         <v>0.1567940562963486</v>
@@ -1167,7 +1167,7 @@
         <v>0.4966996610164642</v>
       </c>
       <c r="K18" t="n">
-        <v>2.74648999998135e-05</v>
+        <v>7.708769999999276e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1183,14 +1183,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>507.47 (11.75)</t>
+          <t>507.47</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>23.63750839233398</v>
+        <v>23.51717827987671</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9937584400177002</v>
+        <v>0.9937585085034371</v>
       </c>
       <c r="F19" t="n">
         <v>0.05372297763824463</v>
@@ -1208,7 +1208,7 @@
         <v>0.4683510661125183</v>
       </c>
       <c r="K19" t="n">
-        <v>2.500250000002779e-05</v>
+        <v>6.122069999992163e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1224,20 +1224,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>538.26 (12.35)</t>
+          <t>538.26</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>23.53730010986328</v>
+        <v>23.42326930809021</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9988589286804199</v>
+        <v>0.9988589948415756</v>
       </c>
       <c r="F20" t="n">
         <v>0.02712249755859375</v>
       </c>
       <c r="G20" t="n">
-        <v>4.438744144863449e-05</v>
+        <v>4.438743781065568e-05</v>
       </c>
       <c r="H20" t="n">
         <v>0.154791846871376</v>
@@ -1249,7 +1249,7 @@
         <v>0.5770438313484192</v>
       </c>
       <c r="K20" t="n">
-        <v>2.797599999985323e-05</v>
+        <v>6.734749999986889e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1265,14 +1265,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>508.94 (11.78)</t>
+          <t>508.94</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>23.64083862304688</v>
+        <v>23.52109443283081</v>
       </c>
       <c r="E21" t="n">
-        <v>1.001208066940308</v>
+        <v>1.001208133876324</v>
       </c>
       <c r="F21" t="n">
         <v>0.05245053768157959</v>
@@ -1290,7 +1290,7 @@
         <v>0.461920827627182</v>
       </c>
       <c r="K21" t="n">
-        <v>2.744580000035057e-05</v>
+        <v>6.907249999994747e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1476.18 (30.48)</t>
+          <t>1476.18</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>23.81794548034668</v>
+        <v>23.75065569877625</v>
       </c>
       <c r="E22" t="n">
-        <v>1.52560818195343</v>
+        <v>1.525608213186264</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0840756893157959</v>
+        <v>0.08184193003177642</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0002366854023421183</v>
+        <v>0.0002366854242427508</v>
       </c>
       <c r="H22" t="n">
         <v>0.1557507812976837</v>
@@ -1331,7 +1331,7 @@
         <v>0.7016832232475281</v>
       </c>
       <c r="K22" t="n">
-        <v>2.449520000027405e-05</v>
+        <v>7.0527200000015e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1474.20 (30.45)</t>
+          <t>1474.20</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23.53760719299316</v>
+        <v>23.4040977973938</v>
       </c>
       <c r="E23" t="n">
-        <v>1.556927442550659</v>
+        <v>1.556927510380745</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0399777889251709</v>
+        <v>0.03917700958251953</v>
       </c>
       <c r="G23" t="n">
-        <v>5.17265907546971e-05</v>
+        <v>5.172658716037404e-05</v>
       </c>
       <c r="H23" t="n">
         <v>0.1535110473632812</v>
@@ -1372,7 +1372,7 @@
         <v>0.6908981204032898</v>
       </c>
       <c r="K23" t="n">
-        <v>2.776889999995546e-05</v>
+        <v>6.699729999991178e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1388,20 +1388,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1462.25 (30.22)</t>
+          <t>1462.25</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>23.45073699951172</v>
+        <v>23.31545826911926</v>
       </c>
       <c r="E24" t="n">
-        <v>1.541547894477844</v>
+        <v>1.541547814965248</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03861665725708008</v>
+        <v>0.03758621740341186</v>
       </c>
       <c r="G24" t="n">
-        <v>8.153536327881739e-05</v>
+        <v>8.153535885503516e-05</v>
       </c>
       <c r="H24" t="n">
         <v>0.1589006781578064</v>
@@ -1413,7 +1413,7 @@
         <v>0.6801029443740845</v>
       </c>
       <c r="K24" t="n">
-        <v>2.727639999966414e-05</v>
+        <v>0.00010253640000019</v>
       </c>
     </row>
     <row r="25">
@@ -1429,20 +1429,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1473.26 (30.43)</t>
+          <t>1473.26</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>23.57296180725098</v>
+        <v>23.44529162216186</v>
       </c>
       <c r="E25" t="n">
-        <v>1.554420590400696</v>
+        <v>1.554420544505119</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03562498092651367</v>
+        <v>0.03438831961154937</v>
       </c>
       <c r="G25" t="n">
-        <v>6.184795347508043e-05</v>
+        <v>6.184796040906803e-05</v>
       </c>
       <c r="H25" t="n">
         <v>0.1514368206262589</v>
@@ -1454,7 +1454,7 @@
         <v>0.6816705465316772</v>
       </c>
       <c r="K25" t="n">
-        <v>2.432610000005297e-05</v>
+        <v>8.704239999997299e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1470,20 +1470,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1467.56 (30.35)</t>
+          <t>1467.56</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>23.46786499023438</v>
+        <v>23.38723732948303</v>
       </c>
       <c r="E26" t="n">
-        <v>1.550407528877258</v>
+        <v>1.550407477140427</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04247593879699707</v>
+        <v>0.04120595920085907</v>
       </c>
       <c r="G26" t="n">
-        <v>5.108834011480212e-05</v>
+        <v>5.108834058773937e-05</v>
       </c>
       <c r="H26" t="n">
         <v>0.1514802873134613</v>
@@ -1495,7 +1495,212 @@
         <v>0.7020230889320374</v>
       </c>
       <c r="K26" t="n">
-        <v>2.806380000038189e-05</v>
+        <v>7.753920000004654e-05</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Run 1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-414.22</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1.303841326713562</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.139754760876298</v>
+      </c>
+      <c r="F27" t="n">
+        <v>55.51378791809082</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.366605536878109</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.110573291778564</v>
+      </c>
+      <c r="I27" t="n">
+        <v>8.361770629882812</v>
+      </c>
+      <c r="J27" t="n">
+        <v>7.057586193084717</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.29290999998193e-05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Run 2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>-445.46</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1.557302371144295</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.1389514054507017</v>
+      </c>
+      <c r="F28" t="n">
+        <v>54.79400964355469</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.3605768283903599</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7282389998435974</v>
+      </c>
+      <c r="I28" t="n">
+        <v>8.910998344421387</v>
+      </c>
+      <c r="J28" t="n">
+        <v>6.389560699462891</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.173479999986739e-05</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Run 3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>-419.15</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2.25095676112175</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.1438932372629642</v>
+      </c>
+      <c r="F29" t="n">
+        <v>55.03629825592041</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.3654956216812134</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6686834096908569</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8.436922073364258</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6.823403835296631</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.364979999969364e-05</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Run 4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>-390.34</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1.71346942281723</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.1432943100035191</v>
+      </c>
+      <c r="F30" t="n">
+        <v>52.46627867889404</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.379814119130373</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.6345776915550232</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7.873542785644531</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7.613820552825928</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.095189999976355e-05</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Run 5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-456.67</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1.651177136421204</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.1400542482584715</v>
+      </c>
+      <c r="F31" t="n">
+        <v>52.82998859786987</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3440113921165466</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6851645708084106</v>
+      </c>
+      <c r="I31" t="n">
+        <v>9.061633110046387</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5.76558780670166</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.303260000029695e-05</v>
       </c>
     </row>
   </sheetData>

--- a/300.xlsx
+++ b/300.xlsx
@@ -486,32 +486,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>517.82</t>
+          <t>54.01 (2.98)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.5144716129303</v>
+        <v>1.880121231079102</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9816862769126892</v>
+        <v>0.1314669400453568</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8765786870718002</v>
+        <v>25.95231628417969</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03664525984227657</v>
+        <v>0.0622643306851387</v>
       </c>
       <c r="H2" t="n">
         <v>1.03788697719574</v>
       </c>
       <c r="I2" t="n">
-        <v>7.925816059112549</v>
+        <v>4.05094051361084</v>
       </c>
       <c r="J2" t="n">
         <v>0.4524632692337036</v>
       </c>
       <c r="K2" t="n">
-        <v>5.51408999999694e-05</v>
+        <v>1.639969999814639e-05</v>
       </c>
     </row>
     <row r="3">
@@ -527,32 +527,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>543.47</t>
+          <t>54.29 (2.98)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.50281911277771</v>
+        <v>1.90410041809082</v>
       </c>
       <c r="E3" t="n">
-        <v>1.009835240721703</v>
+        <v>0.1434856653213501</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8767573237419128</v>
+        <v>25.08394241333008</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03745225444436073</v>
+        <v>0.06386964023113251</v>
       </c>
       <c r="H3" t="n">
         <v>0.5733728408813477</v>
       </c>
       <c r="I3" t="n">
-        <v>8.144954681396484</v>
+        <v>4.084092617034912</v>
       </c>
       <c r="J3" t="n">
         <v>0.4351803958415985</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001060106999998425</v>
+        <v>1.13091999955941e-05</v>
       </c>
     </row>
     <row r="4">
@@ -568,32 +568,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>568.33</t>
+          <t>53.91 (2.98)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.5105962600708</v>
+        <v>1.888992309570312</v>
       </c>
       <c r="E4" t="n">
-        <v>1.047832258105278</v>
+        <v>0.1508659422397614</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8638807884454727</v>
+        <v>25.65898132324219</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0390591447763145</v>
+        <v>0.06562582403421402</v>
       </c>
       <c r="H4" t="n">
         <v>0.7450600862503052</v>
       </c>
       <c r="I4" t="n">
-        <v>8.263260841369629</v>
+        <v>4.025252342224121</v>
       </c>
       <c r="J4" t="n">
         <v>0.447928249835968</v>
       </c>
       <c r="K4" t="n">
-        <v>4.161999999996624e-05</v>
+        <v>1.154410000162898e-05</v>
       </c>
     </row>
     <row r="5">
@@ -609,32 +609,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>531.77</t>
+          <t>57.19 (3.04)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>23.50681049728394</v>
+        <v>1.862832069396973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9904959365129471</v>
+        <v>0.1366174519062042</v>
       </c>
       <c r="F5" t="n">
-        <v>0.883599758207798</v>
+        <v>26.19189453125</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04204990343749523</v>
+        <v>0.06748607754707336</v>
       </c>
       <c r="H5" t="n">
         <v>0.9863747954368591</v>
       </c>
       <c r="I5" t="n">
-        <v>7.912121295928955</v>
+        <v>4.073890686035156</v>
       </c>
       <c r="J5" t="n">
         <v>0.4653018116950989</v>
       </c>
       <c r="K5" t="n">
-        <v>3.61920000000282e-05</v>
+        <v>1.092509999580216e-05</v>
       </c>
     </row>
     <row r="6">
@@ -650,32 +650,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>529.48</t>
+          <t>54.18 (2.98)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23.49596078491211</v>
+        <v>1.864253044128418</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9923847692012787</v>
+        <v>0.1373701542615891</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8796173926591874</v>
+        <v>25.11611557006836</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03738335910812021</v>
+        <v>0.06194174289703369</v>
       </c>
       <c r="H6" t="n">
         <v>0.8094307780265808</v>
       </c>
       <c r="I6" t="n">
-        <v>7.999342441558838</v>
+        <v>4.0836501121521</v>
       </c>
       <c r="J6" t="n">
         <v>0.446069210767746</v>
       </c>
       <c r="K6" t="n">
-        <v>3.99029000000155e-05</v>
+        <v>1.164689999859547e-05</v>
       </c>
     </row>
     <row r="7">
@@ -691,32 +691,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>516.51</t>
+          <t>53.84 (2.98)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>305.1650648803711</v>
+        <v>305.2129821777344</v>
       </c>
       <c r="E7" t="n">
-        <v>10.86353600883484</v>
+        <v>10.23504543304443</v>
       </c>
       <c r="F7" t="n">
-        <v>76053.895125</v>
+        <v>76053.8984375</v>
       </c>
       <c r="G7" t="n">
-        <v>47.8879487953186</v>
+        <v>106.4318695068359</v>
       </c>
       <c r="H7" t="n">
         <v>0.5829544067382812</v>
       </c>
       <c r="I7" t="n">
-        <v>8.171643257141113</v>
+        <v>4.070028781890869</v>
       </c>
       <c r="J7" t="n">
         <v>0.4901336133480072</v>
       </c>
       <c r="K7" t="n">
-        <v>3.236859999969966e-05</v>
+        <v>1.077340000483673e-05</v>
       </c>
     </row>
     <row r="8">
@@ -732,32 +732,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>521.19</t>
+          <t>54.28 (2.98)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>300.1035167236328</v>
+        <v>300.1514282226562</v>
       </c>
       <c r="E8" t="n">
-        <v>10.81852273845673</v>
+        <v>10.18630886077881</v>
       </c>
       <c r="F8" t="n">
         <v>73560.59375</v>
       </c>
       <c r="G8" t="n">
-        <v>44.44980621337891</v>
+        <v>104.5393600463867</v>
       </c>
       <c r="H8" t="n">
         <v>0.5830211639404297</v>
       </c>
       <c r="I8" t="n">
-        <v>8.242114067077637</v>
+        <v>4.077640533447266</v>
       </c>
       <c r="J8" t="n">
         <v>0.4944420158863068</v>
       </c>
       <c r="K8" t="n">
-        <v>3.634079999983442e-05</v>
+        <v>1.10768000013195e-05</v>
       </c>
     </row>
     <row r="9">
@@ -773,32 +773,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>520.88</t>
+          <t>53.85 (2.98)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>297.2915965881348</v>
+        <v>297.3395080566406</v>
       </c>
       <c r="E9" t="n">
-        <v>10.81648396587372</v>
+        <v>10.18589878082275</v>
       </c>
       <c r="F9" t="n">
         <v>72244.734375</v>
       </c>
       <c r="G9" t="n">
-        <v>44.34444427490234</v>
+        <v>102.7636184692383</v>
       </c>
       <c r="H9" t="n">
         <v>0.584128201007843</v>
       </c>
       <c r="I9" t="n">
-        <v>8.230216026306152</v>
+        <v>4.071019172668457</v>
       </c>
       <c r="J9" t="n">
         <v>0.4927139282226562</v>
       </c>
       <c r="K9" t="n">
-        <v>3.787669999974242e-05</v>
+        <v>1.050709999981336e-05</v>
       </c>
     </row>
     <row r="10">
@@ -814,32 +814,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>522.77</t>
+          <t>54.17 (2.98)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>301.5276805725098</v>
+        <v>301.5755920410156</v>
       </c>
       <c r="E10" t="n">
-        <v>10.84467466545105</v>
+        <v>10.21479606628418</v>
       </c>
       <c r="F10" t="n">
         <v>74250.671875</v>
       </c>
       <c r="G10" t="n">
-        <v>45.35451889038086</v>
+        <v>104.8787307739258</v>
       </c>
       <c r="H10" t="n">
         <v>0.5810527801513672</v>
       </c>
       <c r="I10" t="n">
-        <v>8.229585647583008</v>
+        <v>4.075637817382812</v>
       </c>
       <c r="J10" t="n">
         <v>0.496104896068573</v>
       </c>
       <c r="K10" t="n">
-        <v>3.695470000002388e-05</v>
+        <v>1.11862000048859e-05</v>
       </c>
     </row>
     <row r="11">
@@ -855,32 +855,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>520.91</t>
+          <t>54.04 (2.98)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>301.5878306884766</v>
+        <v>301.6357421875</v>
       </c>
       <c r="E11" t="n">
-        <v>10.82664805030823</v>
+        <v>10.19517135620117</v>
       </c>
       <c r="F11" t="n">
         <v>74250.3359375</v>
       </c>
       <c r="G11" t="n">
-        <v>45.37547302246094</v>
+        <v>104.7714767456055</v>
       </c>
       <c r="H11" t="n">
         <v>0.5817579030990601</v>
       </c>
       <c r="I11" t="n">
-        <v>8.232712745666504</v>
+        <v>4.074170589447021</v>
       </c>
       <c r="J11" t="n">
         <v>0.4914999008178711</v>
       </c>
       <c r="K11" t="n">
-        <v>4.095939999979237e-05</v>
+        <v>1.126999999542022e-05</v>
       </c>
     </row>
     <row r="12">
@@ -896,32 +896,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>500.87</t>
+          <t>52.11 (2.94)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>310.904331237793</v>
+        <v>310.9536437988281</v>
       </c>
       <c r="E12" t="n">
-        <v>10.87734477138519</v>
+        <v>10.26029491424561</v>
       </c>
       <c r="F12" t="n">
-        <v>78721.37654687501</v>
+        <v>78727.03125</v>
       </c>
       <c r="G12" t="n">
-        <v>49.68900030899048</v>
+        <v>109.2466812133789</v>
       </c>
       <c r="H12" t="n">
         <v>0.5797107815742493</v>
       </c>
       <c r="I12" t="n">
-        <v>8.019648551940918</v>
+        <v>4.06627893447876</v>
       </c>
       <c r="J12" t="n">
         <v>0.4931358695030212</v>
       </c>
       <c r="K12" t="n">
-        <v>4.085250000025553e-05</v>
+        <v>1.104990000021644e-05</v>
       </c>
     </row>
     <row r="13">
@@ -937,32 +937,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>502.11</t>
+          <t>52.10 (2.94)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>313.7385570373535</v>
+        <v>313.7864685058594</v>
       </c>
       <c r="E13" t="n">
-        <v>10.84992753982544</v>
+        <v>10.23055362701416</v>
       </c>
       <c r="F13" t="n">
         <v>79825.828125</v>
       </c>
       <c r="G13" t="n">
-        <v>51.64238357543945</v>
+        <v>110.6959228515625</v>
       </c>
       <c r="H13" t="n">
         <v>0.5763192772865295</v>
       </c>
       <c r="I13" t="n">
-        <v>8.060465812683105</v>
+        <v>4.06849479675293</v>
       </c>
       <c r="J13" t="n">
         <v>0.4937478005886078</v>
       </c>
       <c r="K13" t="n">
-        <v>3.480050000007396e-05</v>
+        <v>1.063799999974435e-05</v>
       </c>
     </row>
     <row r="14">
@@ -978,32 +978,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>504.39</t>
+          <t>52.03 (2.94)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>309.7830821533203</v>
+        <v>309.8309936523438</v>
       </c>
       <c r="E14" t="n">
-        <v>10.90788943195343</v>
+        <v>10.28995609283447</v>
       </c>
       <c r="F14" t="n">
         <v>78250.234375</v>
       </c>
       <c r="G14" t="n">
-        <v>48.18770980834961</v>
+        <v>108.5985870361328</v>
       </c>
       <c r="H14" t="n">
         <v>0.579704761505127</v>
       </c>
       <c r="I14" t="n">
-        <v>8.069007873535156</v>
+        <v>4.064812183380127</v>
       </c>
       <c r="J14" t="n">
         <v>0.496439665555954</v>
       </c>
       <c r="K14" t="n">
-        <v>3.363360000003013e-05</v>
+        <v>1.230759999452857e-05</v>
       </c>
     </row>
     <row r="15">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>505.22</t>
+          <t>52.32 (2.95)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>312.0805675048828</v>
+        <v>312.1284790039062</v>
       </c>
       <c r="E15" t="n">
-        <v>10.8191839094162</v>
+        <v>10.19476222991943</v>
       </c>
       <c r="F15" t="n">
         <v>79110.859375</v>
       </c>
       <c r="G15" t="n">
-        <v>50.72484970092773</v>
+        <v>109.9802017211914</v>
       </c>
       <c r="H15" t="n">
         <v>0.5783921480178833</v>
       </c>
       <c r="I15" t="n">
-        <v>8.105369567871094</v>
+        <v>4.071304321289062</v>
       </c>
       <c r="J15" t="n">
         <v>0.4954337775707245</v>
       </c>
       <c r="K15" t="n">
-        <v>3.952019999996991e-05</v>
+        <v>1.140359999408247e-05</v>
       </c>
     </row>
     <row r="16">
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>501.63</t>
+          <t>52.20 (2.94)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>312.2620555725098</v>
+        <v>312.3099670410156</v>
       </c>
       <c r="E16" t="n">
-        <v>10.86781303405762</v>
+        <v>10.25049209594727</v>
       </c>
       <c r="F16" t="n">
         <v>79263.625</v>
       </c>
       <c r="G16" t="n">
-        <v>50.27366638183594</v>
+        <v>110.1309356689453</v>
       </c>
       <c r="H16" t="n">
         <v>0.5775067806243896</v>
       </c>
       <c r="I16" t="n">
-        <v>8.03843879699707</v>
+        <v>4.068971157073975</v>
       </c>
       <c r="J16" t="n">
         <v>0.4957082271575928</v>
       </c>
       <c r="K16" t="n">
-        <v>3.971510000019407e-05</v>
+        <v>1.121439999405993e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>507.23</t>
+          <t>49.99 (2.90)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>23.51910361099243</v>
+        <v>1.88355827331543</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9941741064786911</v>
+        <v>0.1289083659648895</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05222225189208984</v>
+        <v>0.08585548400878906</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003138000029139221</v>
+        <v>0.0003692743484862149</v>
       </c>
       <c r="H17" t="n">
         <v>0.1645958572626114</v>
       </c>
       <c r="I17" t="n">
-        <v>8.123622894287109</v>
+        <v>4.036202907562256</v>
       </c>
       <c r="J17" t="n">
         <v>0.4611021280288696</v>
       </c>
       <c r="K17" t="n">
-        <v>8.652249999977357e-05</v>
+        <v>2.853089999553049e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1142,32 +1142,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>520.19</t>
+          <t>55.16 (3.00)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>23.51423371505737</v>
+        <v>3.064884185791016</v>
       </c>
       <c r="E18" t="n">
-        <v>1.002053455770016</v>
+        <v>0.1398729681968689</v>
       </c>
       <c r="F18" t="n">
         <v>0.04766607284545898</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0001393374986946583</v>
+        <v>0.0001393374841427431</v>
       </c>
       <c r="H18" t="n">
         <v>0.1567940562963486</v>
       </c>
       <c r="I18" t="n">
-        <v>8.174849510192871</v>
+        <v>4.073913097381592</v>
       </c>
       <c r="J18" t="n">
         <v>0.4966996610164642</v>
       </c>
       <c r="K18" t="n">
-        <v>7.708769999999276e-05</v>
+        <v>2.802680000604596e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>507.47</t>
+          <t>49.32 (2.89)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>23.51717827987671</v>
+        <v>1.884082794189453</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9937585085034371</v>
+        <v>0.1318871676921844</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05372297763824463</v>
+        <v>0.08358383178710938</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003351031336933374</v>
+        <v>0.0004140552773606032</v>
       </c>
       <c r="H19" t="n">
         <v>0.1638828366994858</v>
       </c>
       <c r="I19" t="n">
-        <v>8.063465118408203</v>
+        <v>4.015975475311279</v>
       </c>
       <c r="J19" t="n">
         <v>0.4683510661125183</v>
       </c>
       <c r="K19" t="n">
-        <v>6.122069999992163e-05</v>
+        <v>2.512190000561532e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1224,32 +1224,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>538.26</t>
+          <t>56.62 (3.03)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>23.42326930809021</v>
+        <v>1.878386497497559</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9988589948415756</v>
+        <v>0.1291255503892899</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02712249755859375</v>
+        <v>0.08688926696777344</v>
       </c>
       <c r="G20" t="n">
-        <v>4.438743781065568e-05</v>
+        <v>7.886729872552678e-05</v>
       </c>
       <c r="H20" t="n">
         <v>0.154791846871376</v>
       </c>
       <c r="I20" t="n">
-        <v>8.140093803405762</v>
+        <v>4.015962600708008</v>
       </c>
       <c r="J20" t="n">
         <v>0.5770438313484192</v>
       </c>
       <c r="K20" t="n">
-        <v>6.734749999986889e-05</v>
+        <v>2.634369999577757e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1265,32 +1265,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>508.94</t>
+          <t>49.67 (2.90)</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>23.52109443283081</v>
+        <v>2.073291301727295</v>
       </c>
       <c r="E21" t="n">
-        <v>1.001208133876324</v>
+        <v>0.1356189548969269</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05245053768157959</v>
+        <v>0.129150390625</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003246634732931852</v>
+        <v>0.000438286951975897</v>
       </c>
       <c r="H21" t="n">
         <v>0.1643150001764297</v>
       </c>
       <c r="I21" t="n">
-        <v>8.09903621673584</v>
+        <v>4.025259017944336</v>
       </c>
       <c r="J21" t="n">
         <v>0.461920827627182</v>
       </c>
       <c r="K21" t="n">
-        <v>6.907249999994747e-05</v>
+        <v>2.772209999966435e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1306,32 +1306,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1476.18</t>
+          <t>211.05 (6.02)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>23.75065569877625</v>
+        <v>1.786699295043945</v>
       </c>
       <c r="E22" t="n">
-        <v>1.525608213186264</v>
+        <v>0.04496731609106064</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08184193003177642</v>
+        <v>0.3500175476074219</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0002366854242427508</v>
+        <v>0.0002961682912427932</v>
       </c>
       <c r="H22" t="n">
         <v>0.1557507812976837</v>
       </c>
       <c r="I22" t="n">
-        <v>14.28986644744873</v>
+        <v>4.923871517181396</v>
       </c>
       <c r="J22" t="n">
         <v>0.7016832232475281</v>
       </c>
       <c r="K22" t="n">
-        <v>7.0527200000015e-05</v>
+        <v>2.445459999580635e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1347,32 +1347,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1474.20</t>
+          <t>202.20 (5.85)</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23.4040977973938</v>
+        <v>1.881559371948242</v>
       </c>
       <c r="E23" t="n">
-        <v>1.556927510380745</v>
+        <v>0.05180619284510612</v>
       </c>
       <c r="F23" t="n">
-        <v>0.03917700958251953</v>
+        <v>0.3162269592285156</v>
       </c>
       <c r="G23" t="n">
-        <v>5.172658716037404e-05</v>
+        <v>8.538585825590417e-05</v>
       </c>
       <c r="H23" t="n">
         <v>0.1535110473632812</v>
       </c>
       <c r="I23" t="n">
-        <v>14.24219417572021</v>
+        <v>4.742875099182129</v>
       </c>
       <c r="J23" t="n">
         <v>0.6908981204032898</v>
       </c>
       <c r="K23" t="n">
-        <v>6.699729999991178e-05</v>
+        <v>2.640439999959199e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1388,32 +1388,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1462.25</t>
+          <t>199.95 (5.80)</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>23.31545826911926</v>
+        <v>1.837547302246094</v>
       </c>
       <c r="E24" t="n">
-        <v>1.541547814965248</v>
+        <v>0.04982857778668404</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03758621740341186</v>
+        <v>0.424224853515625</v>
       </c>
       <c r="G24" t="n">
-        <v>8.153535885503516e-05</v>
+        <v>0.0001413870631949976</v>
       </c>
       <c r="H24" t="n">
         <v>0.1589006781578064</v>
       </c>
       <c r="I24" t="n">
-        <v>14.13094139099121</v>
+        <v>4.735274314880371</v>
       </c>
       <c r="J24" t="n">
         <v>0.6801029443740845</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00010253640000019</v>
+        <v>2.731910000147764e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1429,32 +1429,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1473.26</t>
+          <t>201.77 (5.84)</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>23.44529162216186</v>
+        <v>1.832057952880859</v>
       </c>
       <c r="E25" t="n">
-        <v>1.554420544505119</v>
+        <v>0.04894013330340385</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03438831961154937</v>
+        <v>0.6231155395507812</v>
       </c>
       <c r="G25" t="n">
-        <v>6.184796040906803e-05</v>
+        <v>0.0001767883804859594</v>
       </c>
       <c r="H25" t="n">
         <v>0.1514368206262589</v>
       </c>
       <c r="I25" t="n">
-        <v>14.18090915679932</v>
+        <v>4.741871356964111</v>
       </c>
       <c r="J25" t="n">
         <v>0.6816705465316772</v>
       </c>
       <c r="K25" t="n">
-        <v>8.704239999997299e-05</v>
+        <v>2.679329999955371e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1470,32 +1470,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1467.56</t>
+          <t>202.47 (5.86)</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>23.38723732948303</v>
+        <v>1.888849258422852</v>
       </c>
       <c r="E26" t="n">
-        <v>1.550407477140427</v>
+        <v>0.04867209494113922</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04120595920085907</v>
+        <v>0.4951019287109375</v>
       </c>
       <c r="G26" t="n">
-        <v>5.108834058773937e-05</v>
+        <v>0.0001172899283119477</v>
       </c>
       <c r="H26" t="n">
         <v>0.1514802873134613</v>
       </c>
       <c r="I26" t="n">
-        <v>14.17725944519043</v>
+        <v>4.745369434356689</v>
       </c>
       <c r="J26" t="n">
         <v>0.7020230889320374</v>
       </c>
       <c r="K26" t="n">
-        <v>7.753920000004654e-05</v>
+        <v>2.588269999978365e-05</v>
       </c>
     </row>
     <row r="27">
@@ -1511,20 +1511,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-414.22</t>
+          <t>-414.22 (6.08)</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.303841326713562</v>
+        <v>1.959968566894531</v>
       </c>
       <c r="E27" t="n">
-        <v>0.139754760876298</v>
+        <v>0.1397547721862793</v>
       </c>
       <c r="F27" t="n">
-        <v>55.51378791809082</v>
+        <v>57.04796981811523</v>
       </c>
       <c r="G27" t="n">
-        <v>0.366605536878109</v>
+        <v>0.8222265839576721</v>
       </c>
       <c r="H27" t="n">
         <v>1.110573291778564</v>
@@ -1536,7 +1536,7 @@
         <v>7.057586193084717</v>
       </c>
       <c r="K27" t="n">
-        <v>3.29290999998193e-05</v>
+        <v>9.808000002522022e-06</v>
       </c>
     </row>
     <row r="28">
@@ -1552,20 +1552,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-445.46</t>
+          <t>-445.46 (6.68)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.557302371144295</v>
+        <v>1.884649276733398</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1389514054507017</v>
+        <v>0.1389514058828354</v>
       </c>
       <c r="F28" t="n">
-        <v>54.79400964355469</v>
+        <v>59.15735244750977</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3605768283903599</v>
+        <v>0.8365247249603271</v>
       </c>
       <c r="H28" t="n">
         <v>0.7282389998435974</v>
@@ -1577,7 +1577,7 @@
         <v>6.389560699462891</v>
       </c>
       <c r="K28" t="n">
-        <v>3.173479999986739e-05</v>
+        <v>1.058100000227569e-05</v>
       </c>
     </row>
     <row r="29">
@@ -1593,20 +1593,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-419.15</t>
+          <t>-419.15 (6.17)</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2.25095676112175</v>
+        <v>2.51403284072876</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1438932372629642</v>
+        <v>0.1438932418823242</v>
       </c>
       <c r="F29" t="n">
-        <v>55.03629825592041</v>
+        <v>56.82831192016602</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3654956216812134</v>
+        <v>0.8231838941574097</v>
       </c>
       <c r="H29" t="n">
         <v>0.6686834096908569</v>
@@ -1618,7 +1618,7 @@
         <v>6.823403835296631</v>
       </c>
       <c r="K29" t="n">
-        <v>3.364979999969364e-05</v>
+        <v>1.002039999730187e-05</v>
       </c>
     </row>
     <row r="30">
@@ -1634,20 +1634,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-390.34</t>
+          <t>-390.34 (5.62)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.71346942281723</v>
+        <v>1.976420760154724</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1432943100035191</v>
+        <v>0.1432943046092987</v>
       </c>
       <c r="F30" t="n">
-        <v>52.46627867889404</v>
+        <v>61.13581085205078</v>
       </c>
       <c r="G30" t="n">
-        <v>0.379814119130373</v>
+        <v>0.8147158026695251</v>
       </c>
       <c r="H30" t="n">
         <v>0.6345776915550232</v>
@@ -1659,7 +1659,7 @@
         <v>7.613820552825928</v>
       </c>
       <c r="K30" t="n">
-        <v>3.095189999976355e-05</v>
+        <v>9.575399999448564e-06</v>
       </c>
     </row>
     <row r="31">
@@ -1675,20 +1675,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-456.67</t>
+          <t>-456.67 (6.90)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.651177136421204</v>
+        <v>1.919321060180664</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1400542482584715</v>
+        <v>0.1400542408227921</v>
       </c>
       <c r="F31" t="n">
-        <v>52.82998859786987</v>
+        <v>58.99168395996094</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3440113921165466</v>
+        <v>0.8102849125862122</v>
       </c>
       <c r="H31" t="n">
         <v>0.6851645708084106</v>
@@ -1700,7 +1700,7 @@
         <v>5.76558780670166</v>
       </c>
       <c r="K31" t="n">
-        <v>3.303260000029695e-05</v>
+        <v>9.952799999155104e-06</v>
       </c>
     </row>
   </sheetData>

--- a/300.xlsx
+++ b/300.xlsx
@@ -486,20 +486,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>54.01 (2.98)</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.880121231079102</v>
+        <v>0.8744479451775551</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1314669400453568</v>
+        <v>0.1314669410064817</v>
       </c>
       <c r="F2" t="n">
-        <v>25.95231628417969</v>
+        <v>25.95222457122803</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0622643306851387</v>
+        <v>0.06226431910693646</v>
       </c>
       <c r="H2" t="n">
         <v>1.03788697719574</v>
@@ -511,7 +511,7 @@
         <v>0.4524632692337036</v>
       </c>
       <c r="K2" t="n">
-        <v>1.639969999814639e-05</v>
+        <v>3.045079999719746e-05</v>
       </c>
     </row>
     <row r="3">
@@ -527,20 +527,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>54.29 (2.98)</t>
+          <t>54.29</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.90410041809082</v>
+        <v>1.280601298093796</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1434856653213501</v>
+        <v>0.1434856628924608</v>
       </c>
       <c r="F3" t="n">
         <v>25.08394241333008</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06386964023113251</v>
+        <v>0.06386963278055191</v>
       </c>
       <c r="H3" t="n">
         <v>0.5733728408813477</v>
@@ -552,7 +552,7 @@
         <v>0.4351803958415985</v>
       </c>
       <c r="K3" t="n">
-        <v>1.13091999955941e-05</v>
+        <v>2.346229999966454e-05</v>
       </c>
     </row>
     <row r="4">
@@ -568,20 +568,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>53.91 (2.98)</t>
+          <t>53.91</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.888992309570312</v>
+        <v>1.161942298054695</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1508659422397614</v>
+        <v>0.1508659467846155</v>
       </c>
       <c r="F4" t="n">
-        <v>25.65898132324219</v>
+        <v>25.64643212127686</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06562582403421402</v>
+        <v>0.06562581938505173</v>
       </c>
       <c r="H4" t="n">
         <v>0.7450600862503052</v>
@@ -593,7 +593,7 @@
         <v>0.447928249835968</v>
       </c>
       <c r="K4" t="n">
-        <v>1.154410000162898e-05</v>
+        <v>2.533380000386387e-05</v>
       </c>
     </row>
     <row r="5">
@@ -609,20 +609,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.19 (3.04)</t>
+          <t>57.19</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.862832069396973</v>
+        <v>1.121372854351997</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1366174519062042</v>
+        <v>0.1366174549907446</v>
       </c>
       <c r="F5" t="n">
-        <v>26.19189453125</v>
+        <v>26.18488356781006</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06748607754707336</v>
+        <v>0.06748608157783746</v>
       </c>
       <c r="H5" t="n">
         <v>0.9863747954368591</v>
@@ -634,7 +634,7 @@
         <v>0.4653018116950989</v>
       </c>
       <c r="K5" t="n">
-        <v>1.092509999580216e-05</v>
+        <v>2.401210000243736e-05</v>
       </c>
     </row>
     <row r="6">
@@ -650,20 +650,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>54.18 (2.98)</t>
+          <t>54.18</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.864253044128418</v>
+        <v>0.8809815381765366</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1373701542615891</v>
+        <v>0.1373701484650373</v>
       </c>
       <c r="F6" t="n">
-        <v>25.11611557006836</v>
+        <v>25.11076128005982</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06194174289703369</v>
+        <v>0.06194174175709486</v>
       </c>
       <c r="H6" t="n">
         <v>0.8094307780265808</v>
@@ -675,7 +675,7 @@
         <v>0.446069210767746</v>
       </c>
       <c r="K6" t="n">
-        <v>1.164689999859547e-05</v>
+        <v>2.570540000306209e-05</v>
       </c>
     </row>
     <row r="7">
@@ -691,20 +691,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.84 (2.98)</t>
+          <t>53.84</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>305.2129821777344</v>
+        <v>305.1650648803711</v>
       </c>
       <c r="E7" t="n">
-        <v>10.23504543304443</v>
+        <v>10.23504529953003</v>
       </c>
       <c r="F7" t="n">
-        <v>76053.8984375</v>
+        <v>76053.895125</v>
       </c>
       <c r="G7" t="n">
-        <v>106.4318695068359</v>
+        <v>106.431881477356</v>
       </c>
       <c r="H7" t="n">
         <v>0.5829544067382812</v>
@@ -716,7 +716,7 @@
         <v>0.4901336133480072</v>
       </c>
       <c r="K7" t="n">
-        <v>1.077340000483673e-05</v>
+        <v>2.651959999639075e-05</v>
       </c>
     </row>
     <row r="8">
@@ -732,20 +732,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>54.28 (2.98)</t>
+          <t>54.28</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>300.1514282226562</v>
+        <v>300.1035167236328</v>
       </c>
       <c r="E8" t="n">
-        <v>10.18630886077881</v>
+        <v>10.18630936336517</v>
       </c>
       <c r="F8" t="n">
         <v>73560.59375</v>
       </c>
       <c r="G8" t="n">
-        <v>104.5393600463867</v>
+        <v>104.5393371582031</v>
       </c>
       <c r="H8" t="n">
         <v>0.5830211639404297</v>
@@ -757,7 +757,7 @@
         <v>0.4944420158863068</v>
       </c>
       <c r="K8" t="n">
-        <v>1.10768000013195e-05</v>
+        <v>2.550569999584695e-05</v>
       </c>
     </row>
     <row r="9">
@@ -773,14 +773,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>53.85 (2.98)</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>297.3395080566406</v>
+        <v>297.2915965881348</v>
       </c>
       <c r="E9" t="n">
-        <v>10.18589878082275</v>
+        <v>10.18589804267883</v>
       </c>
       <c r="F9" t="n">
         <v>72244.734375</v>
@@ -798,7 +798,7 @@
         <v>0.4927139282226562</v>
       </c>
       <c r="K9" t="n">
-        <v>1.050709999981336e-05</v>
+        <v>3.213050000340445e-05</v>
       </c>
     </row>
     <row r="10">
@@ -814,14 +814,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>54.17 (2.98)</t>
+          <t>54.17</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>301.5755920410156</v>
+        <v>301.5276805725098</v>
       </c>
       <c r="E10" t="n">
-        <v>10.21479606628418</v>
+        <v>10.21479614448547</v>
       </c>
       <c r="F10" t="n">
         <v>74250.671875</v>
@@ -839,7 +839,7 @@
         <v>0.496104896068573</v>
       </c>
       <c r="K10" t="n">
-        <v>1.11862000048859e-05</v>
+        <v>2.341080000041984e-05</v>
       </c>
     </row>
     <row r="11">
@@ -855,20 +855,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>54.04 (2.98)</t>
+          <t>54.04</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>301.6357421875</v>
+        <v>301.5878306884766</v>
       </c>
       <c r="E11" t="n">
-        <v>10.19517135620117</v>
+        <v>10.19517171859741</v>
       </c>
       <c r="F11" t="n">
         <v>74250.3359375</v>
       </c>
       <c r="G11" t="n">
-        <v>104.7714767456055</v>
+        <v>104.7714691162109</v>
       </c>
       <c r="H11" t="n">
         <v>0.5817579030990601</v>
@@ -880,7 +880,7 @@
         <v>0.4914999008178711</v>
       </c>
       <c r="K11" t="n">
-        <v>1.126999999542022e-05</v>
+        <v>2.535229999921285e-05</v>
       </c>
     </row>
     <row r="12">
@@ -896,20 +896,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>52.11 (2.94)</t>
+          <t>52.11</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>310.9536437988281</v>
+        <v>310.904331237793</v>
       </c>
       <c r="E12" t="n">
-        <v>10.26029491424561</v>
+        <v>10.26029536533356</v>
       </c>
       <c r="F12" t="n">
-        <v>78727.03125</v>
+        <v>78721.37654687501</v>
       </c>
       <c r="G12" t="n">
-        <v>109.2466812133789</v>
+        <v>109.2466761703491</v>
       </c>
       <c r="H12" t="n">
         <v>0.5797107815742493</v>
@@ -921,7 +921,7 @@
         <v>0.4931358695030212</v>
       </c>
       <c r="K12" t="n">
-        <v>1.104990000021644e-05</v>
+        <v>2.679989999887766e-05</v>
       </c>
     </row>
     <row r="13">
@@ -937,14 +937,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>52.10 (2.94)</t>
+          <t>52.10</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>313.7864685058594</v>
+        <v>313.7385570373535</v>
       </c>
       <c r="E13" t="n">
-        <v>10.23055362701416</v>
+        <v>10.23055294513702</v>
       </c>
       <c r="F13" t="n">
         <v>79825.828125</v>
@@ -962,7 +962,7 @@
         <v>0.4937478005886078</v>
       </c>
       <c r="K13" t="n">
-        <v>1.063799999974435e-05</v>
+        <v>2.355260000331327e-05</v>
       </c>
     </row>
     <row r="14">
@@ -978,14 +978,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>52.03 (2.94)</t>
+          <t>52.03</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>309.8309936523438</v>
+        <v>309.7830821533203</v>
       </c>
       <c r="E14" t="n">
-        <v>10.28995609283447</v>
+        <v>10.28995585441589</v>
       </c>
       <c r="F14" t="n">
         <v>78250.234375</v>
@@ -1003,7 +1003,7 @@
         <v>0.496439665555954</v>
       </c>
       <c r="K14" t="n">
-        <v>1.230759999452857e-05</v>
+        <v>2.434180000273045e-05</v>
       </c>
     </row>
     <row r="15">
@@ -1019,20 +1019,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>52.32 (2.95)</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>312.1284790039062</v>
+        <v>312.0805675048828</v>
       </c>
       <c r="E15" t="n">
-        <v>10.19476222991943</v>
+        <v>10.19476198196411</v>
       </c>
       <c r="F15" t="n">
         <v>79110.859375</v>
       </c>
       <c r="G15" t="n">
-        <v>109.9802017211914</v>
+        <v>109.9802093505859</v>
       </c>
       <c r="H15" t="n">
         <v>0.5783921480178833</v>
@@ -1044,7 +1044,7 @@
         <v>0.4954337775707245</v>
       </c>
       <c r="K15" t="n">
-        <v>1.140359999408247e-05</v>
+        <v>2.461529999709455e-05</v>
       </c>
     </row>
     <row r="16">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>52.20 (2.94)</t>
+          <t>52.20</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>312.3099670410156</v>
+        <v>312.2620555725098</v>
       </c>
       <c r="E16" t="n">
-        <v>10.25049209594727</v>
+        <v>10.25049273681641</v>
       </c>
       <c r="F16" t="n">
         <v>79263.625</v>
       </c>
       <c r="G16" t="n">
-        <v>110.1309356689453</v>
+        <v>110.1309280395508</v>
       </c>
       <c r="H16" t="n">
         <v>0.5775067806243896</v>
@@ -1085,7 +1085,7 @@
         <v>0.4957082271575928</v>
       </c>
       <c r="K16" t="n">
-        <v>1.121439999405993e-05</v>
+        <v>2.434350000112317e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1101,20 +1101,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>49.99 (2.90)</t>
+          <t>49.99</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.88355827331543</v>
+        <v>0.8651379157304764</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1289083659648895</v>
+        <v>0.1289083555117249</v>
       </c>
       <c r="F17" t="n">
         <v>0.08585548400878906</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003692743484862149</v>
+        <v>0.0003692743193823844</v>
       </c>
       <c r="H17" t="n">
         <v>0.1645958572626114</v>
@@ -1126,7 +1126,7 @@
         <v>0.4611021280288696</v>
       </c>
       <c r="K17" t="n">
-        <v>2.853089999553049e-05</v>
+        <v>5.33995000005234e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1142,20 +1142,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>55.16 (3.00)</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>3.064884185791016</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1398729681968689</v>
+        <v>0.1398729822635651</v>
       </c>
       <c r="F18" t="n">
         <v>0.04766607284545898</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0001393374841427431</v>
+        <v>0.0001393374986946583</v>
       </c>
       <c r="H18" t="n">
         <v>0.1567940562963486</v>
@@ -1167,7 +1167,7 @@
         <v>0.4966996610164642</v>
       </c>
       <c r="K18" t="n">
-        <v>2.802680000604596e-05</v>
+        <v>5.561880000459496e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1183,20 +1183,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>49.32 (2.89)</t>
+          <t>49.32</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.884082794189453</v>
+        <v>1.034767761766911</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1318871676921844</v>
+        <v>0.1318871736228466</v>
       </c>
       <c r="F19" t="n">
         <v>0.08358383178710938</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004140552773606032</v>
+        <v>0.0004140552482567728</v>
       </c>
       <c r="H19" t="n">
         <v>0.1638828366994858</v>
@@ -1208,7 +1208,7 @@
         <v>0.4683510661125183</v>
       </c>
       <c r="K19" t="n">
-        <v>2.512190000561532e-05</v>
+        <v>5.309960000158753e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1224,20 +1224,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>56.62 (3.03)</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.878386497497559</v>
+        <v>1.590276239871979</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1291255503892899</v>
+        <v>0.1291255493089557</v>
       </c>
       <c r="F20" t="n">
         <v>0.08688926696777344</v>
       </c>
       <c r="G20" t="n">
-        <v>7.886729872552678e-05</v>
+        <v>7.886730600148439e-05</v>
       </c>
       <c r="H20" t="n">
         <v>0.154791846871376</v>
@@ -1249,7 +1249,7 @@
         <v>0.5770438313484192</v>
       </c>
       <c r="K20" t="n">
-        <v>2.634369999577757e-05</v>
+        <v>5.607839999720454e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1265,14 +1265,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>49.67 (2.90)</t>
+          <t>49.67</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>2.073291301727295</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1356189548969269</v>
+        <v>0.1356189649254084</v>
       </c>
       <c r="F21" t="n">
         <v>0.129150390625</v>
@@ -1290,7 +1290,7 @@
         <v>0.461920827627182</v>
       </c>
       <c r="K21" t="n">
-        <v>2.772209999966435e-05</v>
+        <v>5.652279999776511e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>211.05 (6.02)</t>
+          <t>211.05</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.786699295043945</v>
+        <v>1.600064238190651</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04496731609106064</v>
+        <v>0.04496731362119317</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3500175476074219</v>
+        <v>0.1266025346517563</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0002961682912427932</v>
+        <v>0.0002961683030735003</v>
       </c>
       <c r="H22" t="n">
         <v>0.1557507812976837</v>
@@ -1331,7 +1331,7 @@
         <v>0.7016832232475281</v>
       </c>
       <c r="K22" t="n">
-        <v>2.445459999580635e-05</v>
+        <v>5.261109999992186e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>202.20 (5.85)</t>
+          <t>202.20</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.881559371948242</v>
+        <v>1.549118191123009</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05180619284510612</v>
+        <v>0.05180619426816702</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3162269592285156</v>
+        <v>0.07042863237857819</v>
       </c>
       <c r="G23" t="n">
-        <v>8.538585825590417e-05</v>
+        <v>8.538586286886129e-05</v>
       </c>
       <c r="H23" t="n">
         <v>0.1535110473632812</v>
@@ -1372,7 +1372,7 @@
         <v>0.6908981204032898</v>
       </c>
       <c r="K23" t="n">
-        <v>2.640439999959199e-05</v>
+        <v>5.769279999367427e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1388,20 +1388,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>199.95 (5.80)</t>
+          <t>199.95</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.837547302246094</v>
+        <v>1.329763406395912</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04982857778668404</v>
+        <v>0.04982857622951269</v>
       </c>
       <c r="F24" t="n">
-        <v>0.424224853515625</v>
+        <v>0.1119909474849701</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0001413870631949976</v>
+        <v>0.0001413870709729963</v>
       </c>
       <c r="H24" t="n">
         <v>0.1589006781578064</v>
@@ -1413,7 +1413,7 @@
         <v>0.6801029443740845</v>
       </c>
       <c r="K24" t="n">
-        <v>2.731910000147764e-05</v>
+        <v>6.392260000575334e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1429,20 +1429,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>201.77 (5.84)</t>
+          <t>201.77</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.832057952880859</v>
+        <v>1.294627738833428</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04894013330340385</v>
+        <v>0.04894013079255819</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6231155395507812</v>
+        <v>0.1844335215091705</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001767883804859594</v>
+        <v>0.0001767883817592519</v>
       </c>
       <c r="H25" t="n">
         <v>0.1514368206262589</v>
@@ -1454,7 +1454,7 @@
         <v>0.6816705465316772</v>
       </c>
       <c r="K25" t="n">
-        <v>2.679329999955371e-05</v>
+        <v>5.171340000379132e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1470,20 +1470,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>202.47 (5.86)</t>
+          <t>202.47</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.888849258422852</v>
+        <v>1.261105443120003</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04867209494113922</v>
+        <v>0.04867209402471781</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4951019287109375</v>
+        <v>0.1133569221496582</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0001172899283119477</v>
+        <v>0.0001172899328266794</v>
       </c>
       <c r="H26" t="n">
         <v>0.1514802873134613</v>
@@ -1495,7 +1495,7 @@
         <v>0.7020230889320374</v>
       </c>
       <c r="K26" t="n">
-        <v>2.588269999978365e-05</v>
+        <v>8.16465000025346e-05</v>
       </c>
     </row>
     <row r="27">
@@ -1511,20 +1511,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-414.22 (6.08)</t>
+          <t>-414.22</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.959968566894531</v>
+        <v>1.303841326713562</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1397547721862793</v>
+        <v>0.139754760876298</v>
       </c>
       <c r="F27" t="n">
-        <v>57.04796981811523</v>
+        <v>57.00469737243652</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8222265839576721</v>
+        <v>0.8222265567779541</v>
       </c>
       <c r="H27" t="n">
         <v>1.110573291778564</v>
@@ -1536,7 +1536,7 @@
         <v>7.057586193084717</v>
       </c>
       <c r="K27" t="n">
-        <v>9.808000002522022e-06</v>
+        <v>2.413449999585282e-05</v>
       </c>
     </row>
     <row r="28">
@@ -1552,20 +1552,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-445.46 (6.68)</t>
+          <t>-445.46</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.884649276733398</v>
+        <v>1.557302371144295</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1389514058828354</v>
+        <v>0.1389514054507017</v>
       </c>
       <c r="F28" t="n">
-        <v>59.15735244750977</v>
+        <v>59.15734728622436</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8365247249603271</v>
+        <v>0.8365248802900315</v>
       </c>
       <c r="H28" t="n">
         <v>0.7282389998435974</v>
@@ -1577,7 +1577,7 @@
         <v>6.389560699462891</v>
       </c>
       <c r="K28" t="n">
-        <v>1.058100000227569e-05</v>
+        <v>2.468869999574963e-05</v>
       </c>
     </row>
     <row r="29">
@@ -1593,20 +1593,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-419.15 (6.17)</t>
+          <t>-419.15</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2.51403284072876</v>
+        <v>2.25095676112175</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1438932418823242</v>
+        <v>0.1438932372629642</v>
       </c>
       <c r="F29" t="n">
-        <v>56.82831192016602</v>
+        <v>56.81038026809692</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8231838941574097</v>
+        <v>0.8231838847994805</v>
       </c>
       <c r="H29" t="n">
         <v>0.6686834096908569</v>
@@ -1618,7 +1618,7 @@
         <v>6.823403835296631</v>
       </c>
       <c r="K29" t="n">
-        <v>1.002039999730187e-05</v>
+        <v>4.300870000588474e-05</v>
       </c>
     </row>
     <row r="30">
@@ -1634,20 +1634,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-390.34 (5.62)</t>
+          <t>-390.34</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.976420760154724</v>
+        <v>1.71346942281723</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1432943046092987</v>
+        <v>0.1432943100035191</v>
       </c>
       <c r="F30" t="n">
-        <v>61.13581085205078</v>
+        <v>61.09737724304199</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8147158026695251</v>
+        <v>0.8147157391905785</v>
       </c>
       <c r="H30" t="n">
         <v>0.6345776915550232</v>
@@ -1659,7 +1659,7 @@
         <v>7.613820552825928</v>
       </c>
       <c r="K30" t="n">
-        <v>9.575399999448564e-06</v>
+        <v>2.36053000044194e-05</v>
       </c>
     </row>
     <row r="31">
@@ -1675,20 +1675,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-456.67 (6.90)</t>
+          <t>-456.67</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.919321060180664</v>
+        <v>1.651177136421204</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1400542408227921</v>
+        <v>0.1400542482584715</v>
       </c>
       <c r="F31" t="n">
-        <v>58.99168395996094</v>
+        <v>58.92994637680054</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8102849125862122</v>
+        <v>0.8102849712371826</v>
       </c>
       <c r="H31" t="n">
         <v>0.6851645708084106</v>
@@ -1700,7 +1700,7 @@
         <v>5.76558780670166</v>
       </c>
       <c r="K31" t="n">
-        <v>9.952799999155104e-06</v>
+        <v>2.008280000154628e-05</v>
       </c>
     </row>
   </sheetData>

--- a/300.xlsx
+++ b/300.xlsx
@@ -511,7 +511,7 @@
         <v>0.4524632692337036</v>
       </c>
       <c r="K2" t="n">
-        <v>3.045079999719746e-05</v>
+        <v>5.215300000418211e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.4351803958415985</v>
       </c>
       <c r="K3" t="n">
-        <v>2.346229999966454e-05</v>
+        <v>1.350309999543242e-05</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.447928249835968</v>
       </c>
       <c r="K4" t="n">
-        <v>2.533380000386387e-05</v>
+        <v>2.332839999871794e-05</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.4653018116950989</v>
       </c>
       <c r="K5" t="n">
-        <v>2.401210000243736e-05</v>
+        <v>2.293330000247806e-05</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.446069210767746</v>
       </c>
       <c r="K6" t="n">
-        <v>2.570540000306209e-05</v>
+        <v>1.336589999846183e-05</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.4901336133480072</v>
       </c>
       <c r="K7" t="n">
-        <v>2.651959999639075e-05</v>
+        <v>1.27375000010943e-05</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.4944420158863068</v>
       </c>
       <c r="K8" t="n">
-        <v>2.550569999584695e-05</v>
+        <v>1.373929999681423e-05</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.4927139282226562</v>
       </c>
       <c r="K9" t="n">
-        <v>3.213050000340445e-05</v>
+        <v>1.284350000059931e-05</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.496104896068573</v>
       </c>
       <c r="K10" t="n">
-        <v>2.341080000041984e-05</v>
+        <v>1.33265999975265e-05</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.4914999008178711</v>
       </c>
       <c r="K11" t="n">
-        <v>2.535229999921285e-05</v>
+        <v>1.54194999995525e-05</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.4931358695030212</v>
       </c>
       <c r="K12" t="n">
-        <v>2.679989999887766e-05</v>
+        <v>1.298690000112401e-05</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.4937478005886078</v>
       </c>
       <c r="K13" t="n">
-        <v>2.355260000331327e-05</v>
+        <v>1.208180000685388e-05</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.496439665555954</v>
       </c>
       <c r="K14" t="n">
-        <v>2.434180000273045e-05</v>
+        <v>1.250249999429798e-05</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.4954337775707245</v>
       </c>
       <c r="K15" t="n">
-        <v>2.461529999709455e-05</v>
+        <v>1.279290000093169e-05</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.4957082271575928</v>
       </c>
       <c r="K16" t="n">
-        <v>2.434350000112317e-05</v>
+        <v>1.20046000010916e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.4611021280288696</v>
       </c>
       <c r="K17" t="n">
-        <v>5.33995000005234e-05</v>
+        <v>2.71126000006916e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.4966996610164642</v>
       </c>
       <c r="K18" t="n">
-        <v>5.561880000459496e-05</v>
+        <v>2.742279999802122e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.4683510661125183</v>
       </c>
       <c r="K19" t="n">
-        <v>5.309960000158753e-05</v>
+        <v>2.683149999938905e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.5770438313484192</v>
       </c>
       <c r="K20" t="n">
-        <v>5.607839999720454e-05</v>
+        <v>2.592259999801172e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.461920827627182</v>
       </c>
       <c r="K21" t="n">
-        <v>5.652279999776511e-05</v>
+        <v>2.698309999686899e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.7016832232475281</v>
       </c>
       <c r="K22" t="n">
-        <v>5.261109999992186e-05</v>
+        <v>2.544900000066264e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.6908981204032898</v>
       </c>
       <c r="K23" t="n">
-        <v>5.769279999367427e-05</v>
+        <v>2.958209999633255e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.6801029443740845</v>
       </c>
       <c r="K24" t="n">
-        <v>6.392260000575334e-05</v>
+        <v>2.772790000017267e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.6816705465316772</v>
       </c>
       <c r="K25" t="n">
-        <v>5.171340000379132e-05</v>
+        <v>2.550180000253022e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.7020230889320374</v>
       </c>
       <c r="K26" t="n">
-        <v>8.16465000025346e-05</v>
+        <v>2.685729999939213e-05</v>
       </c>
     </row>
     <row r="27">
@@ -1536,7 +1536,7 @@
         <v>7.057586193084717</v>
       </c>
       <c r="K27" t="n">
-        <v>2.413449999585282e-05</v>
+        <v>9.883700004138518e-06</v>
       </c>
     </row>
     <row r="28">
@@ -1577,7 +1577,7 @@
         <v>6.389560699462891</v>
       </c>
       <c r="K28" t="n">
-        <v>2.468869999574963e-05</v>
+        <v>1.182870000047842e-05</v>
       </c>
     </row>
     <row r="29">
@@ -1618,7 +1618,7 @@
         <v>6.823403835296631</v>
       </c>
       <c r="K29" t="n">
-        <v>4.300870000588474e-05</v>
+        <v>1.026000000274507e-05</v>
       </c>
     </row>
     <row r="30">
@@ -1659,7 +1659,7 @@
         <v>7.613820552825928</v>
       </c>
       <c r="K30" t="n">
-        <v>2.36053000044194e-05</v>
+        <v>1.012669999909122e-05</v>
       </c>
     </row>
     <row r="31">
@@ -1700,7 +1700,7 @@
         <v>5.76558780670166</v>
       </c>
       <c r="K31" t="n">
-        <v>2.008280000154628e-05</v>
+        <v>1.042219999362715e-05</v>
       </c>
     </row>
   </sheetData>
